--- a/Excel/BootstrapData.xlsx
+++ b/Excel/BootstrapData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
   <si>
     <t>&lt;/summary&gt;</t>
   </si>
@@ -43,19 +43,10 @@
     <t>SceneInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">LocaleSettings </t>
-  </si>
-  <si>
-    <t>BootstrapLocale</t>
-  </si>
-  <si>
-    <t>BootstrapLocale_{0}</t>
-  </si>
-  <si>
-    <t>ErrorMsgLocale</t>
-  </si>
-  <si>
-    <t>ErrorMsgLocale_{0}</t>
+    <t>LocaleSettings</t>
+  </si>
+  <si>
+    <t>SplashEntryInfo</t>
   </si>
 </sst>
 </file>
@@ -331,7 +322,8 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="20.13"/>
-    <col customWidth="1" min="2" max="3" width="15.13"/>
+    <col customWidth="1" min="2" max="2" width="15.13"/>
+    <col customWidth="1" min="3" max="3" width="19.0"/>
     <col customWidth="1" min="4" max="4" width="39.63"/>
     <col customWidth="1" min="5" max="7" width="20.13"/>
     <col customWidth="1" min="8" max="8" width="22.63"/>
@@ -454,7 +446,6 @@
       <c r="I7" s="3"/>
     </row>
     <row r="8">
-      <c r="A8" s="3"/>
       <c r="B8" s="6">
         <v>6.0</v>
       </c>
@@ -462,30 +453,13 @@
         <v>11</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+        <v>11</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3"/>
-      <c r="B9" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
     </row>
     <row r="10">
       <c r="A10" s="3"/>

--- a/Excel/BootstrapData.xlsx
+++ b/Excel/BootstrapData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>&lt;/summary&gt;</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>SplashEntryInfo</t>
+  </si>
+  <si>
+    <t>AssetInfoEntryBoot</t>
   </si>
 </sst>
 </file>
@@ -457,15 +460,21 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+      <c r="B9" s="6">
+        <v>7.0</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
